--- a/a_materials/Tentative Schedule.xlsx
+++ b/a_materials/Tentative Schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adamsoliman/Documents/GitHub/Econometrics-Slides/a_materials/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{199CFA3F-271E-AF4B-8BF0-33EDF89890DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECA9276B-AB0D-A644-A43E-D21D81694435}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="700" windowWidth="27040" windowHeight="15180" xr2:uid="{72D0DB20-A265-EC45-9D54-DA8133B16545}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="21">
   <si>
     <t>Introduction</t>
   </si>
@@ -64,9 +64,6 @@
     <t>Regression Discontinuity</t>
   </si>
   <si>
-    <t>Difference-in-Differences</t>
-  </si>
-  <si>
     <t>Panel Data</t>
   </si>
   <si>
@@ -95,6 +92,12 @@
   </si>
   <si>
     <t>NO CLASS (Election Day)</t>
+  </si>
+  <si>
+    <t>Difference-in-Differences + Panel Data</t>
+  </si>
+  <si>
+    <t>Check in</t>
   </si>
 </sst>
 </file>
@@ -497,10 +500,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
@@ -605,7 +608,7 @@
         <v>46294</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -641,7 +644,7 @@
         <v>46308</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -650,7 +653,7 @@
         <v>46310</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
@@ -668,7 +671,7 @@
         <v>46317</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -677,7 +680,7 @@
         <v>46322</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
@@ -686,7 +689,7 @@
         <v>46324</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -695,7 +698,7 @@
         <v>46329</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
@@ -704,7 +707,7 @@
         <v>46331</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="25" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -713,7 +716,7 @@
         <v>46336</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="26" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -722,7 +725,7 @@
         <v>46338</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
@@ -731,7 +734,7 @@
         <v>46343</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
@@ -740,7 +743,7 @@
         <v>46345</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="29" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -749,7 +752,7 @@
         <v>46350</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="30" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -758,7 +761,7 @@
         <v>46352</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="31" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -767,7 +770,7 @@
         <v>46357</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="32" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -776,7 +779,7 @@
         <v>46359</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/a_materials/Tentative Schedule.xlsx
+++ b/a_materials/Tentative Schedule.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adamsoliman/Documents/GitHub/Econometrics-Slides/a_materials/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECA9276B-AB0D-A644-A43E-D21D81694435}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A3F1D5C-C9CF-4942-B8D1-958108B96CA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="700" windowWidth="27040" windowHeight="15180" xr2:uid="{72D0DB20-A265-EC45-9D54-DA8133B16545}"/>
+    <workbookView xWindow="-4340" yWindow="-21100" windowWidth="38400" windowHeight="21100" xr2:uid="{72D0DB20-A265-EC45-9D54-DA8133B16545}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="22">
   <si>
     <t>Introduction</t>
   </si>
@@ -94,10 +94,13 @@
     <t>NO CLASS (Election Day)</t>
   </si>
   <si>
-    <t>Difference-in-Differences + Panel Data</t>
-  </si>
-  <si>
-    <t>Check in</t>
+    <t>Multiple Linear Regression (V)</t>
+  </si>
+  <si>
+    <t>Guest Lecture (V)</t>
+  </si>
+  <si>
+    <t>Difference-in-Differences</t>
   </si>
 </sst>
 </file>
@@ -563,7 +566,7 @@
         <v>46275</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
@@ -662,7 +665,7 @@
         <v>46315</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
@@ -680,7 +683,7 @@
         <v>46322</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
@@ -689,7 +692,7 @@
         <v>46324</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.2">

--- a/a_materials/Tentative Schedule.xlsx
+++ b/a_materials/Tentative Schedule.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adamsoliman/Documents/GitHub/Econometrics-Slides/a_materials/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A3F1D5C-C9CF-4942-B8D1-958108B96CA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A98D5DA9-B3D1-5F44-98DC-BD829DE3E439}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-4340" yWindow="-21100" windowWidth="38400" windowHeight="21100" xr2:uid="{72D0DB20-A265-EC45-9D54-DA8133B16545}"/>
+    <workbookView xWindow="0" yWindow="700" windowWidth="27040" windowHeight="15180" xr2:uid="{72D0DB20-A265-EC45-9D54-DA8133B16545}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -97,10 +97,10 @@
     <t>Multiple Linear Regression (V)</t>
   </si>
   <si>
-    <t>Guest Lecture (V)</t>
-  </si>
-  <si>
-    <t>Difference-in-Differences</t>
+    <t>Guest Lecture</t>
+  </si>
+  <si>
+    <t>Difference-in-Differences (V)</t>
   </si>
 </sst>
 </file>
@@ -674,7 +674,7 @@
         <v>46317</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -682,8 +682,8 @@
         <f t="shared" si="0"/>
         <v>46322</v>
       </c>
-      <c r="B21" s="4" t="s">
-        <v>21</v>
+      <c r="B21" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
